--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/johansen_Etanol_IPCA_Brasil.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/johansen_Etanol_IPCA_Brasil.xlsx
@@ -440,7 +440,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>156.5293109836556</v>
+        <v>156.5293109836551</v>
       </c>
       <c r="B2" t="n">
         <v>120.3673</v>
@@ -454,7 +454,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98.0756947076642</v>
+        <v>98.0756947076637</v>
       </c>
       <c r="B3" t="n">
         <v>91.10899999999999</v>
@@ -468,7 +468,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66.52483945372903</v>
+        <v>66.52483945372909</v>
       </c>
       <c r="B4" t="n">
         <v>65.8202</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>40.66323351510631</v>
+        <v>40.66323351510627</v>
       </c>
       <c r="B5" t="n">
         <v>44.4929</v>
@@ -496,7 +496,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21.70477026687043</v>
+        <v>21.70477026687038</v>
       </c>
       <c r="B6" t="n">
         <v>27.0669</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9.421883939991234</v>
+        <v>9.421883939991233</v>
       </c>
       <c r="B7" t="n">
         <v>13.4294</v>
@@ -524,7 +524,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.682514162454894</v>
+        <v>1.682514162454922</v>
       </c>
       <c r="B8" t="n">
         <v>2.7055</v>
